--- a/excell/ALCO LLC_Aminol_PDS data_ industrial gear oil.xlsx
+++ b/excell/ALCO LLC_Aminol_PDS data_ industrial gear oil.xlsx
@@ -1,33 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Aminol_label data\Last\Last updated_12.12.2023\Aminol_PDS_database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aytac M\Documents\GitHub\Aminol\excell\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB25B9B-2397-46D8-B15B-9883266AEAE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Industrial gear oil" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="75">
   <si>
     <t>Product ID</t>
   </si>
@@ -283,11 +276,14 @@
   <si>
     <t>Aminol™ GearSynth 100 is suitable for application in industrial transmissions, where roller and plain bearings are subjected to high pressure and also for large-scale plants with pressure-feed lubrication systems.</t>
   </si>
+  <si>
+    <t>Performance</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -430,7 +426,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -440,7 +436,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -680,28 +676,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:L17"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="17.44140625" customWidth="1"/>
-    <col min="3" max="3" width="35.33203125" customWidth="1"/>
-    <col min="4" max="4" width="47.6640625" customWidth="1"/>
-    <col min="5" max="5" width="41.33203125" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" customWidth="1"/>
+    <col min="3" max="3" width="35.28515625" customWidth="1"/>
+    <col min="4" max="4" width="47.7109375" customWidth="1"/>
+    <col min="5" max="5" width="41.28515625" customWidth="1"/>
     <col min="6" max="6" width="42" customWidth="1"/>
     <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="32.109375" customWidth="1"/>
-    <col min="9" max="9" width="26.88671875" customWidth="1"/>
-    <col min="10" max="10" width="30.44140625" customWidth="1"/>
-    <col min="11" max="11" width="31.109375" style="4" customWidth="1"/>
-    <col min="12" max="12" width="29.77734375" customWidth="1"/>
+    <col min="8" max="8" width="32.140625" customWidth="1"/>
+    <col min="9" max="9" width="26.85546875" customWidth="1"/>
+    <col min="10" max="10" width="30.42578125" customWidth="1"/>
+    <col min="11" max="11" width="31.140625" style="4" customWidth="1"/>
+    <col min="12" max="12" width="29.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
@@ -717,7 +713,9 @@
       <c r="F2" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="G2" s="7"/>
+      <c r="G2" s="7" t="s">
+        <v>74</v>
+      </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
@@ -726,7 +724,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
       <c r="D3" s="9"/>
@@ -749,7 +747,7 @@
       </c>
       <c r="L3" s="9"/>
     </row>
-    <row r="4" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
@@ -784,7 +782,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
@@ -819,7 +817,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
         <v>19</v>
       </c>
@@ -854,7 +852,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
         <v>20</v>
       </c>
@@ -889,7 +887,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
         <v>21</v>
       </c>
@@ -924,7 +922,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
         <v>22</v>
       </c>
@@ -959,7 +957,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
         <v>23</v>
       </c>
@@ -994,7 +992,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
@@ -1029,7 +1027,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="3" t="s">
         <v>30</v>
       </c>
@@ -1064,7 +1062,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
@@ -1099,7 +1097,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
         <v>25</v>
       </c>
@@ -1134,7 +1132,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
         <v>26</v>
       </c>
@@ -1169,7 +1167,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="3" t="s">
         <v>27</v>
       </c>
@@ -1204,7 +1202,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="3" t="s">
         <v>28</v>
       </c>
